--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0003T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0003T0006Z000C1N18_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>8.97746408792467</v>
       </c>
       <c r="E2" t="n">
-        <v>5.007511974882645</v>
+        <v>4.558139427932152</v>
       </c>
       <c r="F2" t="n">
-        <v>4.988647553825741</v>
+        <v>4.480155243587131</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.61742206118826</v>
+        <v>14.03939465307282</v>
       </c>
       <c r="D3" t="n">
-        <v>18.73034227486357</v>
+        <v>12.6855300599381</v>
       </c>
       <c r="E3" t="n">
-        <v>5.007511974882645</v>
+        <v>4.558139427932152</v>
       </c>
       <c r="F3" t="n">
-        <v>4.988647553825741</v>
+        <v>4.480155243587131</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.1608504878359</v>
+        <v>17.61742206118826</v>
       </c>
       <c r="D4" t="n">
-        <v>13.56627796996582</v>
+        <v>18.73034227486357</v>
       </c>
       <c r="E4" t="n">
-        <v>5.007511974882645</v>
+        <v>4.558139427932152</v>
       </c>
       <c r="F4" t="n">
-        <v>4.988647553825741</v>
+        <v>4.480155243587131</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,23 +576,55 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
+        <v>16.1608504878359</v>
+      </c>
+      <c r="D5" t="n">
+        <v>13.56627796996582</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4.558139427932152</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.480155243587131</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>T12594</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>W0065F0003T0006Z000C1N18.png</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
         <v>6.409809242485164</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D6" t="n">
         <v>5.436814335216059</v>
       </c>
-      <c r="E5" t="n">
-        <v>5.007511974882645</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4.988647553825741</v>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="E6" t="n">
+        <v>4.558139427932152</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4.480155243587131</v>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>T12594</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0003T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0003T0006Z000C1N18_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.504899360800877</v>
+        <v>1.219546146130143</v>
       </c>
       <c r="D2" t="n">
-        <v>8.97746408792467</v>
+        <v>1.458837914287759</v>
       </c>
       <c r="E2" t="n">
-        <v>4.558139427932152</v>
+        <v>0.7406976570389746</v>
       </c>
       <c r="F2" t="n">
-        <v>4.480155243587131</v>
+        <v>0.7280252270829088</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.03939465307282</v>
+        <v>2.281401631124333</v>
       </c>
       <c r="D3" t="n">
-        <v>12.6855300599381</v>
+        <v>2.061398634739942</v>
       </c>
       <c r="E3" t="n">
-        <v>4.558139427932152</v>
+        <v>0.7406976570389746</v>
       </c>
       <c r="F3" t="n">
-        <v>4.480155243587131</v>
+        <v>0.7280252270829088</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>17.61742206118826</v>
+        <v>2.862831084943093</v>
       </c>
       <c r="D4" t="n">
-        <v>18.73034227486357</v>
+        <v>3.043680619665331</v>
       </c>
       <c r="E4" t="n">
-        <v>4.558139427932152</v>
+        <v>0.7406976570389746</v>
       </c>
       <c r="F4" t="n">
-        <v>4.480155243587131</v>
+        <v>0.7280252270829088</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>16.1608504878359</v>
+        <v>2.626138204273334</v>
       </c>
       <c r="D5" t="n">
-        <v>13.56627796996582</v>
+        <v>2.204520170119445</v>
       </c>
       <c r="E5" t="n">
-        <v>4.558139427932152</v>
+        <v>0.7406976570389746</v>
       </c>
       <c r="F5" t="n">
-        <v>4.480155243587131</v>
+        <v>0.7280252270829088</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>6.409809242485164</v>
+        <v>1.041594001903839</v>
       </c>
       <c r="D6" t="n">
-        <v>5.436814335216059</v>
+        <v>0.8834823294726096</v>
       </c>
       <c r="E6" t="n">
-        <v>4.558139427932152</v>
+        <v>0.7406976570389746</v>
       </c>
       <c r="F6" t="n">
-        <v>4.480155243587131</v>
+        <v>0.7280252270829088</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
